--- a/Rutas Neuquinas - DB.xlsx
+++ b/Rutas Neuquinas - DB.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="204">
   <si>
     <t>ID</t>
   </si>
@@ -22,13 +22,13 @@
     <t>CORREDOR</t>
   </si>
   <si>
-    <t>ORDEN</t>
-  </si>
-  <si>
     <t>NOMBRE</t>
   </si>
   <si>
-    <t>LATITUD - LONGITUD</t>
+    <t>LATITUD</t>
+  </si>
+  <si>
+    <t>LONGITUD</t>
   </si>
   <si>
     <t>TIPO</t>
@@ -49,16 +49,16 @@
     <t>NQN</t>
   </si>
   <si>
-    <t>Neuquén - Las Ovejas</t>
-  </si>
-  <si>
-    <t>010</t>
+    <t>NQN-CCO-BAN-CRI-ZAP-CCU-LAJ-CHO-NAU-CHM-LLA-AND-LOV</t>
   </si>
   <si>
     <t>NEUQUEN</t>
   </si>
   <si>
-    <t>-38.959162, -68.105352</t>
+    <t>-38.959162</t>
+  </si>
+  <si>
+    <t>-68.105352</t>
   </si>
   <si>
     <t>LOCALIDAD</t>
@@ -76,13 +76,13 @@
     <t>CCO</t>
   </si>
   <si>
-    <t>020</t>
-  </si>
-  <si>
     <t>CUTRAL CO</t>
   </si>
   <si>
-    <t>-38.929447, -69.225346</t>
+    <t>-38.929447</t>
+  </si>
+  <si>
+    <t>-69.225346</t>
   </si>
   <si>
     <t>84be6d6b</t>
@@ -91,13 +91,13 @@
     <t>BAN</t>
   </si>
   <si>
-    <t>030</t>
-  </si>
-  <si>
     <t>CERRO BANDERA</t>
   </si>
   <si>
-    <t>-38.957683, -69.454516</t>
+    <t>-38.957683</t>
+  </si>
+  <si>
+    <t>-69.454516</t>
   </si>
   <si>
     <t>PUNTO DE INTERES</t>
@@ -112,13 +112,13 @@
     <t>CRI</t>
   </si>
   <si>
-    <t>040</t>
-  </si>
-  <si>
     <t>CRISTO</t>
   </si>
   <si>
-    <t>-38.882944, -69.992200</t>
+    <t>-38.882944</t>
+  </si>
+  <si>
+    <t>-69.992200</t>
   </si>
   <si>
     <t>0c98f22b</t>
@@ -127,13 +127,13 @@
     <t>ZAP</t>
   </si>
   <si>
-    <t>050</t>
-  </si>
-  <si>
     <t>ZAPALA</t>
   </si>
   <si>
-    <t>-38.890986, -70.042249</t>
+    <t>-38.890986</t>
+  </si>
+  <si>
+    <t>-70.042249</t>
   </si>
   <si>
     <t>4f60d409</t>
@@ -142,13 +142,13 @@
     <t>CCU</t>
   </si>
   <si>
-    <t>060</t>
-  </si>
-  <si>
     <t>CUCHILLO CURA</t>
   </si>
   <si>
-    <t>-38.729965, -70.291256</t>
+    <t>-38.729965</t>
+  </si>
+  <si>
+    <t>-70.291256</t>
   </si>
   <si>
     <t>RN40</t>
@@ -163,13 +163,13 @@
     <t>LAJ</t>
   </si>
   <si>
-    <t>070</t>
-  </si>
-  <si>
     <t>LAS LAJAS</t>
   </si>
   <si>
-    <t>-38.538240, -70.367044</t>
+    <t>-38.538240</t>
+  </si>
+  <si>
+    <t>-70.367044</t>
   </si>
   <si>
     <t>45d404db</t>
@@ -178,13 +178,13 @@
     <t>CHO</t>
   </si>
   <si>
-    <t>080</t>
-  </si>
-  <si>
     <t>CHORRIACA</t>
   </si>
   <si>
-    <t>-37.935096, -70.071818</t>
+    <t>-37.935096</t>
+  </si>
+  <si>
+    <t>-70.071818</t>
   </si>
   <si>
     <t>692046ab</t>
@@ -193,13 +193,13 @@
     <t>NAU</t>
   </si>
   <si>
-    <t>090</t>
-  </si>
-  <si>
     <t>NAUNAUCO</t>
   </si>
   <si>
-    <t>-37.553511, -70.181245</t>
+    <t>-37.553511</t>
+  </si>
+  <si>
+    <t>-70.181245</t>
   </si>
   <si>
     <t>Punto cercano al paraje Naunauco</t>
@@ -211,13 +211,16 @@
     <t>CHM</t>
   </si>
   <si>
-    <t>100</t>
+    <t>NQN-CCO-BAN-CRI-ZAP-CCU-LAJ-CHO-NAU-CHM-LLA-AND-LOV , CHM-CAE-MEN-AQH-CAH-MOL-TRC , CHM-LSA-ARB-CHP-LEU-TRC , HCU-MDL-ECH-RAH-CHM , CHM-TAQ-TAC-TAA-TRA</t>
   </si>
   <si>
     <t>CHOS MALAL</t>
   </si>
   <si>
-    <t>-37.390362, -70.250048</t>
+    <t>-37.390362</t>
+  </si>
+  <si>
+    <t>-70.250048</t>
   </si>
   <si>
     <t>1214cc9d</t>
@@ -226,13 +229,13 @@
     <t>LLA</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>EL LLANO</t>
   </si>
   <si>
-    <t>-37.225047, -70.624545</t>
+    <t>-37.225047</t>
+  </si>
+  <si>
+    <t>-70.624545</t>
   </si>
   <si>
     <t>RP43</t>
@@ -244,13 +247,13 @@
     <t>AND</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>ANDACOLLO</t>
   </si>
   <si>
-    <t>-37.195906, -70.661626</t>
+    <t>-37.195906</t>
+  </si>
+  <si>
+    <t>-70.661626</t>
   </si>
   <si>
     <t>570b4529</t>
@@ -259,13 +262,367 @@
     <t>LOV</t>
   </si>
   <si>
-    <t>130</t>
+    <t>NQN-CCO-BAN-CRI-ZAP-CCU-LAJ-CHO-NAU-CHM-LLA-AND-LOV , LOV-INV-VVC-MAG</t>
   </si>
   <si>
     <t>LAS OVEJAS</t>
   </si>
   <si>
-    <t>-36.990721, -70.749320</t>
+    <t>-36.990721</t>
+  </si>
+  <si>
+    <t>-70.749320</t>
+  </si>
+  <si>
+    <t>108442c8</t>
+  </si>
+  <si>
+    <t>MAG</t>
+  </si>
+  <si>
+    <t>LOV-INV-VVC-MAG</t>
+  </si>
+  <si>
+    <t>MANZANO AMARGO</t>
+  </si>
+  <si>
+    <t>-36.766139</t>
+  </si>
+  <si>
+    <t>-70.756500</t>
+  </si>
+  <si>
+    <t>RP54</t>
+  </si>
+  <si>
+    <t>59194c91</t>
+  </si>
+  <si>
+    <t>VVC</t>
+  </si>
+  <si>
+    <t>VARVARCO</t>
+  </si>
+  <si>
+    <t>-36.858215</t>
+  </si>
+  <si>
+    <t>-70.679828</t>
+  </si>
+  <si>
+    <t>3f63ebdb</t>
+  </si>
+  <si>
+    <t>INV</t>
+  </si>
+  <si>
+    <t>INVERNADA VIEJA</t>
+  </si>
+  <si>
+    <t>-36.910147</t>
+  </si>
+  <si>
+    <t>-70.704268</t>
+  </si>
+  <si>
+    <t>e85d343d</t>
+  </si>
+  <si>
+    <t>LSA</t>
+  </si>
+  <si>
+    <t>CHM-LSA-ARB-CHP-LEU-TRC</t>
+  </si>
+  <si>
+    <t>LA SALADA</t>
+  </si>
+  <si>
+    <t>-37.310633</t>
+  </si>
+  <si>
+    <t>-70.248941</t>
+  </si>
+  <si>
+    <t>5ab5ab1e</t>
+  </si>
+  <si>
+    <t>ARB</t>
+  </si>
+  <si>
+    <t>ARROYO BLANCO</t>
+  </si>
+  <si>
+    <t>-37.243448</t>
+  </si>
+  <si>
+    <t>-70.232371</t>
+  </si>
+  <si>
+    <t>RP2</t>
+  </si>
+  <si>
+    <t>af2376f4</t>
+  </si>
+  <si>
+    <t>CHP</t>
+  </si>
+  <si>
+    <t>CHAPUA</t>
+  </si>
+  <si>
+    <t>-37.182455</t>
+  </si>
+  <si>
+    <t>-70.248613</t>
+  </si>
+  <si>
+    <t>279ffca5</t>
+  </si>
+  <si>
+    <t>LEU</t>
+  </si>
+  <si>
+    <t>LEUTO CABALLO</t>
+  </si>
+  <si>
+    <t>-37.128866</t>
+  </si>
+  <si>
+    <t>-70.258052</t>
+  </si>
+  <si>
+    <t>9e10d844</t>
+  </si>
+  <si>
+    <t>TRC</t>
+  </si>
+  <si>
+    <t>CHM-CAE-MEN-AQH-CAH-MOL-TRC , CHM-LSA-ARB-CHP-LEU-TRC</t>
+  </si>
+  <si>
+    <t>TRICAO MALAL</t>
+  </si>
+  <si>
+    <t>-37.047358</t>
+  </si>
+  <si>
+    <t>-70.327154</t>
+  </si>
+  <si>
+    <t>f46a6293</t>
+  </si>
+  <si>
+    <t>CAE</t>
+  </si>
+  <si>
+    <t>CHM-CAE-MEN-AQH-CAH-MOL-TRC</t>
+  </si>
+  <si>
+    <t>CAEPE MALAL</t>
+  </si>
+  <si>
+    <t>-37.175434</t>
+  </si>
+  <si>
+    <t>-70.395780</t>
+  </si>
+  <si>
+    <t>RP41</t>
+  </si>
+  <si>
+    <t>2905b554</t>
+  </si>
+  <si>
+    <t>MEN</t>
+  </si>
+  <si>
+    <t>LOS MENUCOS</t>
+  </si>
+  <si>
+    <t>-37.130060</t>
+  </si>
+  <si>
+    <t>-70.398620</t>
+  </si>
+  <si>
+    <t>e4849fdc</t>
+  </si>
+  <si>
+    <t>AQH</t>
+  </si>
+  <si>
+    <t>AQUIHUECO</t>
+  </si>
+  <si>
+    <t>-37.083568</t>
+  </si>
+  <si>
+    <t>-70.384375</t>
+  </si>
+  <si>
+    <t>fb342c96</t>
+  </si>
+  <si>
+    <t>CAH</t>
+  </si>
+  <si>
+    <t>CANCHA HUINGANCO</t>
+  </si>
+  <si>
+    <t>-37.029683</t>
+  </si>
+  <si>
+    <t>-70.420503</t>
+  </si>
+  <si>
+    <t>e64e5ced</t>
+  </si>
+  <si>
+    <t>MOL</t>
+  </si>
+  <si>
+    <t>MOLULCO</t>
+  </si>
+  <si>
+    <t>-37.002380</t>
+  </si>
+  <si>
+    <t>-70.408835</t>
+  </si>
+  <si>
+    <t>15267c23</t>
+  </si>
+  <si>
+    <t>ECH</t>
+  </si>
+  <si>
+    <t>HCU-MDL-ECH-RAH-CHM</t>
+  </si>
+  <si>
+    <t>EL CHOLAR</t>
+  </si>
+  <si>
+    <t>-37.443338</t>
+  </si>
+  <si>
+    <t>-70.628787</t>
+  </si>
+  <si>
+    <t>RP6</t>
+  </si>
+  <si>
+    <t>02cf491e</t>
+  </si>
+  <si>
+    <t>HCU</t>
+  </si>
+  <si>
+    <t>EL HUECU</t>
+  </si>
+  <si>
+    <t>-37.646875</t>
+  </si>
+  <si>
+    <t>-70.591736</t>
+  </si>
+  <si>
+    <t>RP21</t>
+  </si>
+  <si>
+    <t>3c56bce7</t>
+  </si>
+  <si>
+    <t>MDL</t>
+  </si>
+  <si>
+    <t>MANDOLEHUE</t>
+  </si>
+  <si>
+    <t>-37.563985</t>
+  </si>
+  <si>
+    <t>-70.642858</t>
+  </si>
+  <si>
+    <t>a79211a1</t>
+  </si>
+  <si>
+    <t>RAH</t>
+  </si>
+  <si>
+    <t>RAHUECO</t>
+  </si>
+  <si>
+    <t>-37.395334</t>
+  </si>
+  <si>
+    <t>-70.408347</t>
+  </si>
+  <si>
+    <t>63e8a61b</t>
+  </si>
+  <si>
+    <t>TAQ</t>
+  </si>
+  <si>
+    <t>CHM-TAQ-TAC-TAA-TRA</t>
+  </si>
+  <si>
+    <t>TAQUIMILAN ABAJO</t>
+  </si>
+  <si>
+    <t>-37.499600</t>
+  </si>
+  <si>
+    <t>-70.236326</t>
+  </si>
+  <si>
+    <t>RP29</t>
+  </si>
+  <si>
+    <t>6430765d</t>
+  </si>
+  <si>
+    <t>TAC</t>
+  </si>
+  <si>
+    <t>TAQUIMILAN CENTRO</t>
+  </si>
+  <si>
+    <t>-37.563994</t>
+  </si>
+  <si>
+    <t>-70.287831</t>
+  </si>
+  <si>
+    <t>7b1ca0a2</t>
+  </si>
+  <si>
+    <t>TAA</t>
+  </si>
+  <si>
+    <t>TAQUIMILAN ARRIBA</t>
+  </si>
+  <si>
+    <t>-37.585175</t>
+  </si>
+  <si>
+    <t>-70.301747</t>
+  </si>
+  <si>
+    <t>64ac6e9d</t>
+  </si>
+  <si>
+    <t>TRA</t>
+  </si>
+  <si>
+    <t>TRAILATHUE</t>
+  </si>
+  <si>
+    <t>-37.617265</t>
+  </si>
+  <si>
+    <t>-70.298256</t>
   </si>
 </sst>
 </file>
@@ -313,7 +670,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -323,16 +680,12 @@
     <xf quotePrefix="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="4" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf quotePrefix="1" borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf quotePrefix="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="4" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -550,7 +903,8 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="6" max="6" width="38.75"/>
+    <col customWidth="1" min="5" max="5" width="13.5"/>
+    <col customWidth="1" min="6" max="6" width="12.38"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -595,13 +949,13 @@
       <c r="C2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G2" s="1" t="s">
@@ -624,13 +978,13 @@
       <c r="C3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G3" s="1" t="s">
@@ -653,13 +1007,13 @@
       <c r="C4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="2" t="s">
         <v>28</v>
       </c>
       <c r="G4" s="1" t="s">
@@ -682,13 +1036,13 @@
       <c r="C5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>35</v>
       </c>
       <c r="G5" s="1" t="s">
@@ -711,13 +1065,13 @@
       <c r="C6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G6" s="1" t="s">
@@ -740,13 +1094,13 @@
       <c r="C7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>45</v>
       </c>
       <c r="G7" s="1" t="s">
@@ -772,13 +1126,13 @@
       <c r="C8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="2" t="s">
         <v>52</v>
       </c>
       <c r="G8" s="1" t="s">
@@ -801,13 +1155,13 @@
       <c r="C9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="2" t="s">
         <v>57</v>
       </c>
       <c r="G9" s="1" t="s">
@@ -830,13 +1184,13 @@
       <c r="C10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="3" t="s">
         <v>62</v>
       </c>
       <c r="G10" s="1" t="s">
@@ -860,16 +1214,16 @@
         <v>65</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="E11" s="2" t="s">
         <v>68</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>16</v>
@@ -883,28 +1237,28 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E12" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="E12" s="4" t="s">
         <v>73</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>74</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>29</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>30</v>
@@ -912,28 +1266,28 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="E13" s="2" t="s">
         <v>79</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>18</v>
@@ -941,35 +1295,641 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E14" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="D14" s="1" t="s">
         <v>84</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="15">
-      <c r="F15" s="6"/>
+      <c r="A15" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
